--- a/wdio-ts-cucumber/Data/TestData.xlsx
+++ b/wdio-ts-cucumber/Data/TestData.xlsx
@@ -412,7 +412,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>StoreID-XXQM7L</v>
+        <v>StoreID-0YPL89</v>
       </c>
       <c r="B2" t="str">
         <v>pettycashandutilities@pu.com</v>

--- a/wdio-ts-cucumber/Data/TestData.xlsx
+++ b/wdio-ts-cucumber/Data/TestData.xlsx
@@ -412,7 +412,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>StoreID-0YPL89</v>
+        <v>StoreID-YRJGIC</v>
       </c>
       <c r="B2" t="str">
         <v>pettycashandutilities@pu.com</v>
